--- a/EXCEL/class notes/day1&2 basics/First day Basic class_V1.xlsx
+++ b/EXCEL/class notes/day1&2 basics/First day Basic class_V1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day1&amp;2 basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF01105C-F279-4D3C-99E7-890CA42782DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5B5594-DDB1-4CC3-A67A-458EE12CF4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="735" xr2:uid="{41CB78D7-EC91-42F6-B5D7-6C8EB6F8E2A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="735" activeTab="6" xr2:uid="{41CB78D7-EC91-42F6-B5D7-6C8EB6F8E2A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Text related basic formula" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -738,7 +747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -782,11 +791,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1106,18 +1112,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BA95E0-7075-4D65-B2A3-D71D5A8F62CC}">
   <dimension ref="A2:M17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="8.7265625" style="6"/>
-    <col min="4" max="4" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="6"/>
+    <col min="4" max="4" width="18.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D2" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f>LEFT(D2)</f>
         <v>S</v>
@@ -1145,10 +1151,10 @@
         <v>S</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C5" s="13"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f>RIGHT(D2)</f>
         <v>w</v>
@@ -1176,14 +1182,14 @@
         <v>w</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" s="13"/>
       <c r="J7">
         <f>FIND(G12,D2,FIND(G12,D2)+1)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f>MID(D2,8,9)</f>
         <v>test data</v>
@@ -1203,7 +1209,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
@@ -1228,15 +1234,11 @@
         <f>LEN(D2)</f>
         <v>20</v>
       </c>
-      <c r="G10">
-        <f>LEN(D2)</f>
-        <v>20</v>
-      </c>
       <c r="I10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" s="13"/>
       <c r="I11" t="s">
         <v>69</v>
@@ -1254,7 +1256,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" s="13" t="s">
         <v>4</v>
       </c>
@@ -1282,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="L12" s="22" t="e">
-        <f t="shared" ref="K12:M12" si="0">FIND($G$12,$D$2,K12+1)</f>
+        <f t="shared" ref="L12:M12" si="0">FIND($G$12,$D$2,K12+1)</f>
         <v>#VALUE!</v>
       </c>
       <c r="M12" s="22" t="e">
@@ -1290,7 +1292,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" s="13"/>
       <c r="D13" t="s">
         <v>10</v>
@@ -1302,7 +1304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C14" s="13" t="s">
         <v>5</v>
       </c>
@@ -1311,7 +1313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I15" s="1">
         <f>SEARCH($G$12,$D$2)</f>
         <v>2</v>
@@ -1333,12 +1335,12 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="J16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
         <v>74</v>
       </c>
@@ -1351,29 +1353,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3BB8334-34D7-41C0-9E38-1CE5AEBAEE26}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1002</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1003</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1004</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1005</v>
       </c>
@@ -1393,7 +1395,7 @@
         <v>Nme1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1006</v>
       </c>
@@ -1413,7 +1415,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1007</v>
       </c>
@@ -1430,7 +1432,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1008</v>
       </c>
@@ -1447,7 +1449,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1009</v>
       </c>
@@ -1464,7 +1466,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1010</v>
       </c>
@@ -1481,7 +1483,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D11" s="5">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -1495,7 +1497,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D12" s="5">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -1509,7 +1511,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D13" s="5">
         <f t="shared" si="0"/>
         <v>1009</v>
@@ -1523,7 +1525,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D14" s="5">
         <f t="shared" si="0"/>
         <v>1010</v>
@@ -1537,7 +1539,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="G15" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Nme1</v>
@@ -1555,21 +1557,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B42F5D5E-645B-4101-8B2D-0E89AF7D6A41}">
   <dimension ref="A1:P16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G1" t="s">
         <v>57</v>
       </c>
@@ -1577,7 +1579,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="G2">
         <f>LEN(G4)</f>
         <v>3</v>
@@ -1586,7 +1588,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F3" t="s">
         <v>51</v>
       </c>
@@ -1616,7 +1618,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>LEN(F4)</f>
         <v>13</v>
@@ -1650,7 +1652,7 @@
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" ref="A5:A11" si="0">LEN(F5)</f>
         <v>14</v>
@@ -1684,7 +1686,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1718,7 +1720,7 @@
       </c>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1752,7 +1754,7 @@
       </c>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1786,13 +1788,13 @@
       </c>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1810,7 +1812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1832,7 +1834,7 @@
       </c>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D12">
         <f>FIND(" ",F12)</f>
         <v>4</v>
@@ -1860,7 +1862,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D13">
         <f t="shared" ref="D13:D16" si="6">FIND(" ",F13)</f>
         <v>6</v>
@@ -1888,7 +1890,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D14">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -1916,7 +1918,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D15">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -1944,7 +1946,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D16">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -1980,13 +1982,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3723D436-3FD9-44D0-9796-AF7AB44DA15B}">
   <dimension ref="A1:U18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>63</v>
       </c>
@@ -2000,7 +2002,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>1001</v>
       </c>
@@ -2014,7 +2016,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>1002</v>
       </c>
@@ -2022,7 +2024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1003</v>
       </c>
@@ -2036,7 +2038,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>1004</v>
       </c>
@@ -2100,7 +2102,7 @@
         <v>Emp ID</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>1005</v>
       </c>
@@ -2164,7 +2166,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>1006</v>
       </c>
@@ -2228,7 +2230,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>1007</v>
       </c>
@@ -2292,7 +2294,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>1008</v>
       </c>
@@ -2356,7 +2358,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>1009</v>
       </c>
@@ -2420,7 +2422,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>1010</v>
       </c>
@@ -2484,7 +2486,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E12" s="8">
         <f t="shared" si="2"/>
         <v>1007</v>
@@ -2542,7 +2544,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E13" s="8">
         <f t="shared" si="2"/>
         <v>1008</v>
@@ -2600,7 +2602,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E14" s="8">
         <f t="shared" si="2"/>
         <v>1009</v>
@@ -2658,7 +2660,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E15" s="8">
         <f t="shared" si="2"/>
         <v>1010</v>
@@ -2716,7 +2718,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="E16" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2774,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:21" x14ac:dyDescent="0.3">
       <c r="E17" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2832,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="5:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="5:21" x14ac:dyDescent="0.3">
       <c r="E18" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2899,24 +2901,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6083B7B1-E3AD-4AA0-BAB1-D64AB863DA91}">
   <dimension ref="D2:P18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="4:16" x14ac:dyDescent="0.3">
       <c r="L2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D4" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D5" s="18" t="s">
         <v>12</v>
       </c>
@@ -2940,12 +2942,12 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D6" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D7" s="18">
         <v>123</v>
       </c>
@@ -2969,15 +2971,15 @@
       </c>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D8" s="19"/>
     </row>
-    <row r="9" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D9" s="18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D10" s="18" t="s">
         <v>14</v>
       </c>
@@ -3001,18 +3003,18 @@
       </c>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D11" s="18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D12" s="19"/>
       <c r="N12" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D13" s="19"/>
       <c r="F13" t="s">
         <v>25</v>
@@ -3039,7 +3041,7 @@
       </c>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D14" s="18" t="s">
         <v>16</v>
       </c>
@@ -3047,7 +3049,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D15" s="18" t="s">
         <v>76</v>
       </c>
@@ -3056,7 +3058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="4:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D16" s="18">
         <v>1</v>
       </c>
@@ -3065,7 +3067,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:11" x14ac:dyDescent="0.3">
       <c r="D17" s="18">
         <v>2</v>
       </c>
@@ -3073,7 +3075,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="4:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D18" s="20" t="s">
         <v>18</v>
       </c>
@@ -3088,16 +3090,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA26E78-4BD4-4780-B3E1-BBF97EBD5ED8}">
   <dimension ref="C1:P23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.6328125" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="4.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="12" max="12" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C1" s="23"/>
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
@@ -3117,15 +3119,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="29"/>
+      <c r="H2" s="27"/>
       <c r="J2" s="9">
         <v>48</v>
       </c>
@@ -3145,13 +3144,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C3" s="26"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="29"/>
+      <c r="H3" s="27"/>
       <c r="J3" s="9">
         <v>100</v>
       </c>
@@ -3168,18 +3163,15 @@
         <v>Disctinction</v>
       </c>
     </row>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.35">
-      <c r="C4" s="30">
+    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C4" s="28">
         <v>3</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="31" t="str">
+      <c r="F4" s="2" t="str">
         <f>IF(C4&lt;&gt;10,"Not Ten","Ten")</f>
         <v>Not Ten</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="29"/>
+      <c r="H4" s="27"/>
       <c r="J4" s="9">
         <v>15</v>
       </c>
@@ -3202,13 +3194,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C5" s="26"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="29"/>
+      <c r="H5" s="27"/>
       <c r="J5" s="9">
         <v>91</v>
       </c>
@@ -3231,15 +3219,13 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6" s="26"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="32"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="29"/>
       <c r="J6" s="9">
         <v>42</v>
       </c>
@@ -3262,13 +3248,13 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="35"/>
+    <row r="7" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="30"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="32"/>
       <c r="J7" s="9">
         <v>98</v>
       </c>
@@ -3291,7 +3277,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="J8" s="9">
         <v>88</v>
       </c>
@@ -3314,7 +3300,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" s="6" t="s">
         <v>90</v>
       </c>
@@ -3337,7 +3323,7 @@
         <v>Disctinction</v>
       </c>
     </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" s="6" t="s">
         <v>92</v>
       </c>
@@ -3360,7 +3346,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G11" s="2" t="s">
         <v>81</v>
       </c>
@@ -3383,7 +3369,7 @@
         <v>First class</v>
       </c>
     </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G12" s="2" t="s">
         <v>83</v>
       </c>
@@ -3409,7 +3395,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G13" s="2" t="s">
         <v>85</v>
       </c>
@@ -3432,7 +3418,7 @@
         <v>First class</v>
       </c>
     </row>
-    <row r="14" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C14">
         <v>100</v>
       </c>
@@ -3464,7 +3450,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C15">
         <v>100</v>
       </c>
@@ -3484,7 +3470,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="16" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:16" x14ac:dyDescent="0.3">
       <c r="J16" s="9">
         <v>69</v>
       </c>
@@ -3504,7 +3490,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F17">
         <v>321</v>
       </c>
@@ -3515,7 +3501,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F18">
         <v>321</v>
       </c>
@@ -3526,7 +3512,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F19">
         <v>321</v>
       </c>
@@ -3537,7 +3523,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F20">
         <v>321</v>
       </c>
@@ -3548,7 +3534,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F21">
         <v>321</v>
       </c>
@@ -3559,7 +3545,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F22">
         <v>321</v>
       </c>
@@ -3570,7 +3556,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="6:8" x14ac:dyDescent="0.3">
       <c r="F23">
         <v>321</v>
       </c>
@@ -3591,14 +3577,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82AB2C51-5970-4912-873E-6D16D758D214}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
@@ -3630,7 +3616,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -3661,7 +3647,7 @@
       </c>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -3692,7 +3678,7 @@
       </c>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -3723,7 +3709,7 @@
       </c>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -3754,7 +3740,7 @@
       </c>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -3785,7 +3771,7 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E7" s="8">
         <v>5</v>
       </c>
@@ -3804,7 +3790,7 @@
       </c>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E8" s="8">
         <v>5</v>
       </c>
@@ -3823,7 +3809,7 @@
       </c>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E9" s="8">
         <v>3</v>
       </c>
@@ -3842,7 +3828,7 @@
       </c>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E10" s="8">
         <v>4</v>
       </c>
@@ -3861,7 +3847,7 @@
       </c>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E11" s="8">
         <v>1</v>
       </c>
@@ -3880,7 +3866,7 @@
       </c>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E12" s="8">
         <v>3</v>
       </c>
@@ -3899,7 +3885,7 @@
       </c>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E13" s="8">
         <v>3</v>
       </c>
@@ -3918,7 +3904,7 @@
       </c>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E14" s="15">
         <v>10</v>
       </c>
@@ -3928,14 +3914,14 @@
       </c>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E15" s="2"/>
       <c r="F15" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>104</v>
       </c>
